--- a/Elderly_EDA_Summary.xlsx
+++ b/Elderly_EDA_Summary.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10215"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/naghamdaood/Projects/TATOO/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7044F215-D4E0-5A4A-A6DD-2135D6834671}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Demographics" sheetId="1" r:id="rId1"/>
@@ -18,7 +24,7 @@
     <sheet name="T13" sheetId="9" r:id="rId9"/>
     <sheet name="T20" sheetId="10" r:id="rId10"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -1072,8 +1078,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1125,8 +1131,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1136,13 +1145,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1180,7 +1197,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1214,6 +1231,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1248,9 +1266,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1423,11 +1442,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="32.83203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1453,7 +1482,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1461,7 +1490,7 @@
         <v>27</v>
       </c>
       <c r="C2">
-        <v>76.90000000000001</v>
+        <v>76.900000000000006</v>
       </c>
       <c r="D2" t="s">
         <v>13</v>
@@ -1479,7 +1508,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -1487,7 +1516,7 @@
         <v>120</v>
       </c>
       <c r="C3">
-        <v>36.8</v>
+        <v>36.799999999999997</v>
       </c>
       <c r="D3" t="s">
         <v>14</v>
@@ -1505,7 +1534,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -1531,7 +1560,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -1557,7 +1586,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -1565,7 +1594,7 @@
         <v>230</v>
       </c>
       <c r="C6">
-        <v>70.40000000000001</v>
+        <v>70.400000000000006</v>
       </c>
       <c r="D6" t="s">
         <v>17</v>
@@ -1589,35 +1618,35 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:P9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" s="1"/>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1" t="s">
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1" t="s">
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-    </row>
-    <row r="2" spans="1:16">
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1667,17 +1696,17 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>320</v>
       </c>
       <c r="B4">
-        <v>8.109999999999999</v>
+        <v>8.11</v>
       </c>
       <c r="C4">
         <v>14.35</v>
@@ -1722,7 +1751,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>321</v>
       </c>
@@ -1730,7 +1759,7 @@
         <v>3</v>
       </c>
       <c r="C5">
-        <v>2.3</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="D5">
         <v>3</v>
@@ -1772,7 +1801,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>322</v>
       </c>
@@ -1822,7 +1851,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="7" spans="1:16">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>323</v>
       </c>
@@ -1830,7 +1859,7 @@
         <v>2.08</v>
       </c>
       <c r="C7">
-        <v>2.28</v>
+        <v>2.2799999999999998</v>
       </c>
       <c r="D7">
         <v>1.19</v>
@@ -1872,7 +1901,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="8" spans="1:16">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>324</v>
       </c>
@@ -1883,7 +1912,7 @@
         <v>28.16</v>
       </c>
       <c r="D8">
-        <v>9.720000000000001</v>
+        <v>9.7200000000000006</v>
       </c>
       <c r="E8">
         <v>7.62</v>
@@ -1922,7 +1951,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="9" spans="1:16">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>325</v>
       </c>
@@ -1983,35 +2012,35 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:P10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" s="1"/>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1" t="s">
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1" t="s">
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-    </row>
-    <row r="2" spans="1:16">
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -2061,17 +2090,17 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>37</v>
       </c>
       <c r="B4">
-        <v>0.8100000000000001</v>
+        <v>0.81</v>
       </c>
       <c r="C4">
         <v>19.78</v>
@@ -2116,7 +2145,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>38</v>
       </c>
@@ -2124,7 +2153,7 @@
         <v>98.11</v>
       </c>
       <c r="C5">
-        <v>95.90000000000001</v>
+        <v>95.9</v>
       </c>
       <c r="D5" t="s">
         <v>44</v>
@@ -2166,7 +2195,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>39</v>
       </c>
@@ -2198,7 +2227,7 @@
         <v>7.3</v>
       </c>
       <c r="K6">
-        <v>9.949999999999999</v>
+        <v>9.9499999999999993</v>
       </c>
       <c r="L6" t="s">
         <v>47</v>
@@ -2216,7 +2245,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="7" spans="1:16">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>40</v>
       </c>
@@ -2266,7 +2295,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="8" spans="1:16">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>41</v>
       </c>
@@ -2283,7 +2312,7 @@
         <v>78.94</v>
       </c>
       <c r="F8">
-        <v>86.59999999999999</v>
+        <v>86.6</v>
       </c>
       <c r="G8">
         <v>10.8</v>
@@ -2316,12 +2345,12 @@
         <v>69</v>
       </c>
     </row>
-    <row r="9" spans="1:16">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>42</v>
       </c>
       <c r="B9">
-        <v>72.06999999999999</v>
+        <v>72.069999999999993</v>
       </c>
       <c r="C9">
         <v>47.41</v>
@@ -2330,7 +2359,7 @@
         <v>44</v>
       </c>
       <c r="E9">
-        <v>19.58</v>
+        <v>19.579999999999998</v>
       </c>
       <c r="F9">
         <v>10.98</v>
@@ -2366,7 +2395,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="10" spans="1:16">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>43</v>
       </c>
@@ -2374,7 +2403,7 @@
         <v>1.87</v>
       </c>
       <c r="C10">
-        <v>2.18</v>
+        <v>2.1800000000000002</v>
       </c>
       <c r="D10" t="s">
         <v>44</v>
@@ -2398,7 +2427,7 @@
         <v>1.38</v>
       </c>
       <c r="K10">
-        <v>2.49</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="L10" t="s">
         <v>51</v>
@@ -2427,35 +2456,35 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:P13"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" s="1"/>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1" t="s">
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1" t="s">
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-    </row>
-    <row r="2" spans="1:16">
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -2505,12 +2534,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>72</v>
       </c>
@@ -2527,7 +2556,7 @@
         <v>7.84</v>
       </c>
       <c r="F4">
-        <v>8.050000000000001</v>
+        <v>8.0500000000000007</v>
       </c>
       <c r="G4">
         <v>8</v>
@@ -2560,7 +2589,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>73</v>
       </c>
@@ -2583,7 +2612,7 @@
         <v>8.1</v>
       </c>
       <c r="H5">
-        <v>9.880000000000001</v>
+        <v>9.8800000000000008</v>
       </c>
       <c r="I5" t="s">
         <v>44</v>
@@ -2610,7 +2639,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>74</v>
       </c>
@@ -2627,7 +2656,7 @@
         <v>8.26</v>
       </c>
       <c r="F6">
-        <v>8.869999999999999</v>
+        <v>8.8699999999999992</v>
       </c>
       <c r="G6">
         <v>10</v>
@@ -2660,7 +2689,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="7" spans="1:16">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>75</v>
       </c>
@@ -2710,7 +2739,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="8" spans="1:16">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>76</v>
       </c>
@@ -2733,7 +2762,7 @@
         <v>0.6</v>
       </c>
       <c r="H8">
-        <v>9.880000000000001</v>
+        <v>9.8800000000000008</v>
       </c>
       <c r="I8" t="s">
         <v>44</v>
@@ -2760,7 +2789,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="9" spans="1:16">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>77</v>
       </c>
@@ -2777,7 +2806,7 @@
         <v>0.22</v>
       </c>
       <c r="F9">
-        <v>0.8100000000000001</v>
+        <v>0.81</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -2810,7 +2839,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="10" spans="1:16">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>78</v>
       </c>
@@ -2818,7 +2847,7 @@
         <v>24.04</v>
       </c>
       <c r="C10">
-        <v>33.91</v>
+        <v>33.909999999999997</v>
       </c>
       <c r="D10" t="s">
         <v>44</v>
@@ -2860,7 +2889,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="11" spans="1:16">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>79</v>
       </c>
@@ -2910,7 +2939,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="12" spans="1:16">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>80</v>
       </c>
@@ -2960,7 +2989,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="13" spans="1:16">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>81</v>
       </c>
@@ -2968,7 +2997,7 @@
         <v>1.88</v>
       </c>
       <c r="C13">
-        <v>2.28</v>
+        <v>2.2799999999999998</v>
       </c>
       <c r="D13" t="s">
         <v>44</v>
@@ -2989,7 +3018,7 @@
         <v>44</v>
       </c>
       <c r="J13">
-        <v>1.12</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="K13">
         <v>1.73</v>
@@ -3021,35 +3050,35 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:P13"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" s="1"/>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1" t="s">
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1" t="s">
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-    </row>
-    <row r="2" spans="1:16">
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -3099,20 +3128,20 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>115</v>
       </c>
       <c r="B4">
-        <v>9.630000000000001</v>
+        <v>9.6300000000000008</v>
       </c>
       <c r="C4">
-        <v>8.619999999999999</v>
+        <v>8.6199999999999992</v>
       </c>
       <c r="D4">
         <v>10.07</v>
@@ -3154,7 +3183,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>116</v>
       </c>
@@ -3180,7 +3209,7 @@
         <v>25.42</v>
       </c>
       <c r="I5">
-        <v>10.2</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="J5">
         <v>8.1</v>
@@ -3204,7 +3233,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>117</v>
       </c>
@@ -3227,7 +3256,7 @@
         <v>10.6</v>
       </c>
       <c r="H6">
-        <v>17.9</v>
+        <v>17.899999999999999</v>
       </c>
       <c r="I6">
         <v>7.1</v>
@@ -3254,12 +3283,12 @@
         <v>160</v>
       </c>
     </row>
-    <row r="7" spans="1:16">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>118</v>
       </c>
       <c r="B7">
-        <v>16.33</v>
+        <v>16.329999999999998</v>
       </c>
       <c r="C7">
         <v>55.61</v>
@@ -3304,7 +3333,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="8" spans="1:16">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>119</v>
       </c>
@@ -3315,10 +3344,10 @@
         <v>6.39</v>
       </c>
       <c r="D8">
-        <v>0.6899999999999999</v>
+        <v>0.69</v>
       </c>
       <c r="E8">
-        <v>0.6899999999999999</v>
+        <v>0.69</v>
       </c>
       <c r="F8">
         <v>2.17</v>
@@ -3327,7 +3356,7 @@
         <v>0.7</v>
       </c>
       <c r="H8">
-        <v>4.86</v>
+        <v>4.8600000000000003</v>
       </c>
       <c r="I8">
         <v>0.6</v>
@@ -3354,7 +3383,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="9" spans="1:16">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>120</v>
       </c>
@@ -3365,7 +3394,7 @@
         <v>47.11</v>
       </c>
       <c r="D9">
-        <v>0.58</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="E9">
         <v>2.36</v>
@@ -3404,7 +3433,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="10" spans="1:16">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>121</v>
       </c>
@@ -3454,7 +3483,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="11" spans="1:16">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>122</v>
       </c>
@@ -3465,10 +3494,10 @@
         <v>31.65</v>
       </c>
       <c r="D11">
-        <v>85.73999999999999</v>
+        <v>85.74</v>
       </c>
       <c r="E11">
-        <v>79.45999999999999</v>
+        <v>79.459999999999994</v>
       </c>
       <c r="F11">
         <v>83.94</v>
@@ -3504,7 +3533,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="12" spans="1:16">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>123</v>
       </c>
@@ -3554,7 +3583,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="13" spans="1:16">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>124</v>
       </c>
@@ -3615,35 +3644,35 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:P21"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" s="1"/>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1" t="s">
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1" t="s">
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-    </row>
-    <row r="2" spans="1:16">
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -3693,12 +3722,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>165</v>
       </c>
@@ -3709,7 +3738,7 @@
         <v>44</v>
       </c>
       <c r="D4">
-        <v>99.06999999999999</v>
+        <v>99.07</v>
       </c>
       <c r="E4" t="s">
         <v>44</v>
@@ -3748,7 +3777,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>166</v>
       </c>
@@ -3798,7 +3827,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>167</v>
       </c>
@@ -3848,7 +3877,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:16">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>168</v>
       </c>
@@ -3859,7 +3888,7 @@
         <v>44</v>
       </c>
       <c r="D7">
-        <v>8.470000000000001</v>
+        <v>8.4700000000000006</v>
       </c>
       <c r="E7" t="s">
         <v>44</v>
@@ -3898,7 +3927,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:16">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>169</v>
       </c>
@@ -3948,12 +3977,12 @@
         <v>44</v>
       </c>
     </row>
-    <row r="9" spans="1:16">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>170</v>
       </c>
       <c r="B9">
-        <v>0.8100000000000001</v>
+        <v>0.81</v>
       </c>
       <c r="C9" t="s">
         <v>44</v>
@@ -3998,7 +4027,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="10" spans="1:16">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>171</v>
       </c>
@@ -4009,7 +4038,7 @@
         <v>44</v>
       </c>
       <c r="D10">
-        <v>0.8100000000000001</v>
+        <v>0.81</v>
       </c>
       <c r="E10" t="s">
         <v>44</v>
@@ -4048,7 +4077,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="11" spans="1:16">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>172</v>
       </c>
@@ -4098,7 +4127,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="12" spans="1:16">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>173</v>
       </c>
@@ -4148,7 +4177,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="13" spans="1:16">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>174</v>
       </c>
@@ -4198,7 +4227,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:16">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>175</v>
       </c>
@@ -4248,7 +4277,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="15" spans="1:16">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>176</v>
       </c>
@@ -4298,7 +4327,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="16" spans="1:16">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>177</v>
       </c>
@@ -4348,7 +4377,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="17" spans="1:16">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>178</v>
       </c>
@@ -4368,7 +4397,7 @@
         <v>44</v>
       </c>
       <c r="G17">
-        <v>9.699999999999999</v>
+        <v>9.6999999999999993</v>
       </c>
       <c r="H17" t="s">
         <v>44</v>
@@ -4398,7 +4427,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="1:16">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>179</v>
       </c>
@@ -4448,7 +4477,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="19" spans="1:16">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>180</v>
       </c>
@@ -4498,7 +4527,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="20" spans="1:16">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>181</v>
       </c>
@@ -4548,7 +4577,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="21" spans="1:16">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>182</v>
       </c>
@@ -4609,35 +4638,35 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:P23"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" s="1"/>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1" t="s">
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1" t="s">
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-    </row>
-    <row r="2" spans="1:16">
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -4687,17 +4716,17 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>203</v>
       </c>
       <c r="B4">
-        <v>8.039999999999999</v>
+        <v>8.0399999999999991</v>
       </c>
       <c r="C4" t="s">
         <v>44</v>
@@ -4742,7 +4771,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>204</v>
       </c>
@@ -4762,7 +4791,7 @@
         <v>44</v>
       </c>
       <c r="G5">
-        <v>16.15</v>
+        <v>16.149999999999999</v>
       </c>
       <c r="H5" t="s">
         <v>44</v>
@@ -4792,7 +4821,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>205</v>
       </c>
@@ -4803,7 +4832,7 @@
         <v>44</v>
       </c>
       <c r="D6">
-        <v>0.28</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="E6" t="s">
         <v>44</v>
@@ -4842,7 +4871,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:16">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>206</v>
       </c>
@@ -4892,7 +4921,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:16">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>207</v>
       </c>
@@ -4918,7 +4947,7 @@
         <v>44</v>
       </c>
       <c r="I8">
-        <v>20.1</v>
+        <v>20.100000000000001</v>
       </c>
       <c r="J8" t="s">
         <v>44</v>
@@ -4942,7 +4971,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="9" spans="1:16">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>208</v>
       </c>
@@ -4992,7 +5021,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="10" spans="1:16">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>209</v>
       </c>
@@ -5042,7 +5071,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="11" spans="1:16">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>210</v>
       </c>
@@ -5092,7 +5121,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="12" spans="1:16">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>211</v>
       </c>
@@ -5103,7 +5132,7 @@
         <v>44</v>
       </c>
       <c r="D12">
-        <v>91.51000000000001</v>
+        <v>91.51</v>
       </c>
       <c r="E12" t="s">
         <v>44</v>
@@ -5142,18 +5171,18 @@
         <v>44</v>
       </c>
     </row>
-    <row r="13" spans="1:16">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>212</v>
       </c>
       <c r="B13">
-        <v>17.19</v>
+        <v>17.190000000000001</v>
       </c>
       <c r="C13" t="s">
         <v>44</v>
       </c>
       <c r="D13">
-        <v>8.470000000000001</v>
+        <v>8.4700000000000006</v>
       </c>
       <c r="E13" t="s">
         <v>44</v>
@@ -5192,7 +5221,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:16">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>213</v>
       </c>
@@ -5203,7 +5232,7 @@
         <v>44</v>
       </c>
       <c r="D14">
-        <v>8.140000000000001</v>
+        <v>8.14</v>
       </c>
       <c r="E14" t="s">
         <v>44</v>
@@ -5242,7 +5271,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="15" spans="1:16">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>214</v>
       </c>
@@ -5292,7 +5321,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="16" spans="1:16">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>215</v>
       </c>
@@ -5303,7 +5332,7 @@
         <v>44</v>
       </c>
       <c r="D16">
-        <v>0.8100000000000001</v>
+        <v>0.81</v>
       </c>
       <c r="E16" t="s">
         <v>44</v>
@@ -5342,7 +5371,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="17" spans="1:16">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>216</v>
       </c>
@@ -5392,7 +5421,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="1:16">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>217</v>
       </c>
@@ -5403,7 +5432,7 @@
         <v>44</v>
       </c>
       <c r="D18">
-        <v>19.56</v>
+        <v>19.559999999999999</v>
       </c>
       <c r="E18" t="s">
         <v>44</v>
@@ -5418,7 +5447,7 @@
         <v>44</v>
       </c>
       <c r="I18">
-        <v>19.6</v>
+        <v>19.600000000000001</v>
       </c>
       <c r="J18" t="s">
         <v>44</v>
@@ -5442,7 +5471,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="19" spans="1:16">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>218</v>
       </c>
@@ -5492,7 +5521,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="20" spans="1:16">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>219</v>
       </c>
@@ -5542,7 +5571,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="21" spans="1:16">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>220</v>
       </c>
@@ -5592,7 +5621,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="22" spans="1:16">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>221</v>
       </c>
@@ -5642,12 +5671,12 @@
         <v>44</v>
       </c>
     </row>
-    <row r="23" spans="1:16">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>222</v>
       </c>
       <c r="B23">
-        <v>19.58</v>
+        <v>19.579999999999998</v>
       </c>
       <c r="C23" t="s">
         <v>44</v>
@@ -5703,35 +5732,35 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:P12"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" s="1"/>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1" t="s">
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1" t="s">
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-    </row>
-    <row r="2" spans="1:16">
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -5781,12 +5810,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>248</v>
       </c>
@@ -5836,7 +5865,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>249</v>
       </c>
@@ -5886,7 +5915,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>250</v>
       </c>
@@ -5936,7 +5965,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:16">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>251</v>
       </c>
@@ -5986,7 +6015,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:16">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>252</v>
       </c>
@@ -6036,7 +6065,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="9" spans="1:16">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>253</v>
       </c>
@@ -6086,7 +6115,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="10" spans="1:16">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>254</v>
       </c>
@@ -6136,7 +6165,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="11" spans="1:16">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>255</v>
       </c>
@@ -6186,7 +6215,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="12" spans="1:16">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>256</v>
       </c>
@@ -6247,35 +6276,35 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:P10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" s="1"/>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1" t="s">
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1" t="s">
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-    </row>
-    <row r="2" spans="1:16">
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -6325,12 +6354,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>264</v>
       </c>
@@ -6380,7 +6409,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>265</v>
       </c>
@@ -6394,7 +6423,7 @@
         <v>44</v>
       </c>
       <c r="E5">
-        <v>4.9</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="F5">
         <v>4.55</v>
@@ -6430,7 +6459,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>266</v>
       </c>
@@ -6480,7 +6509,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="7" spans="1:16">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>267</v>
       </c>
@@ -6500,7 +6529,7 @@
         <v>4.62</v>
       </c>
       <c r="G7">
-        <v>4.27</v>
+        <v>4.2699999999999996</v>
       </c>
       <c r="H7">
         <v>3.26</v>
@@ -6530,7 +6559,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="8" spans="1:16">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>268</v>
       </c>
@@ -6580,7 +6609,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="9" spans="1:16">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>269</v>
       </c>
@@ -6594,7 +6623,7 @@
         <v>44</v>
       </c>
       <c r="E9">
-        <v>10.21</v>
+        <v>10.210000000000001</v>
       </c>
       <c r="F9">
         <v>23.19</v>
@@ -6609,7 +6638,7 @@
         <v>44</v>
       </c>
       <c r="J9">
-        <v>9.300000000000001</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="K9">
         <v>21.5</v>
@@ -6630,15 +6659,15 @@
         <v>290</v>
       </c>
     </row>
-    <row r="10" spans="1:16">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>270</v>
       </c>
       <c r="B10">
-        <v>19.65</v>
+        <v>19.649999999999999</v>
       </c>
       <c r="C10">
-        <v>18.74</v>
+        <v>18.739999999999998</v>
       </c>
       <c r="D10" t="s">
         <v>44</v>
@@ -6691,35 +6720,35 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:P9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" s="1"/>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1" t="s">
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1" t="s">
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-    </row>
-    <row r="2" spans="1:16">
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -6769,12 +6798,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>292</v>
       </c>
@@ -6824,7 +6853,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>293</v>
       </c>
@@ -6874,7 +6903,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>294</v>
       </c>
@@ -6885,7 +6914,7 @@
         <v>15.36</v>
       </c>
       <c r="D6">
-        <v>20.44</v>
+        <v>20.440000000000001</v>
       </c>
       <c r="E6">
         <v>13.86</v>
@@ -6924,7 +6953,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="7" spans="1:16">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>295</v>
       </c>
@@ -6935,13 +6964,13 @@
         <v>9.4</v>
       </c>
       <c r="D7">
-        <v>4.02</v>
+        <v>4.0199999999999996</v>
       </c>
       <c r="E7">
         <v>4.24</v>
       </c>
       <c r="F7">
-        <v>4.77</v>
+        <v>4.7699999999999996</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -6974,7 +7003,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="8" spans="1:16">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>296</v>
       </c>
@@ -6991,7 +7020,7 @@
         <v>5.98</v>
       </c>
       <c r="F8">
-        <v>8.619999999999999</v>
+        <v>8.6199999999999992</v>
       </c>
       <c r="G8">
         <v>7.22</v>
@@ -7024,7 +7053,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="9" spans="1:16">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>297</v>
       </c>
